--- a/zy72341/data/demo_weights.xlsx
+++ b/zy72341/data/demo_weights.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>weight_id</t>
   </si>
@@ -40,19 +40,37 @@
     <t>W001</t>
   </si>
   <si>
+    <t>W002</t>
+  </si>
+  <si>
     <t>Q2</t>
   </si>
   <si>
+    <t>Q3</t>
+  </si>
+  <si>
     <t>逻辑完整性</t>
   </si>
   <si>
+    <t>答案详实度</t>
+  </si>
+  <si>
     <t>V1.0</t>
   </si>
   <si>
+    <t>V1.5</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>旧口径权重系数，因评分标准调整需补录说明</t>
+    <t>2024-01-15</t>
+  </si>
+  <si>
+    <t>【运营规划阿岚备注】此题为早期命题，2024年1月起评分标准调整为新口径V2.0，V1.0旧标准下的得分需要按0.9系数折算并补录说明，避免新旧口径混算。2024-01-10及之前提交的Q2题均适用。</t>
+  </si>
+  <si>
+    <t>【运营规划阿岚备注】Q3题发现存在答案过短但给分偏高的现象，补录此权重系数用于事后抽检和校准。仅对2024-01-15~01-20期间提交生效。</t>
   </si>
 </sst>
 </file>
@@ -410,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,22 +459,45 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>0.9</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
         <v>12</v>
+      </c>
+      <c r="D3">
+        <v>0.85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
